--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120062035</v>
+        <v>120061827</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503305</v>
+        <v>503337</v>
       </c>
       <c r="R2" t="n">
-        <v>6918716</v>
+        <v>6918753</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120061827</v>
+        <v>120062035</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,41 +799,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503337</v>
+        <v>503305</v>
       </c>
       <c r="R3" t="n">
-        <v>6918753</v>
+        <v>6918716</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120061827</v>
+        <v>120062035</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503337</v>
+        <v>503305</v>
       </c>
       <c r="R2" t="n">
-        <v>6918753</v>
+        <v>6918716</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120062035</v>
+        <v>120061827</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,55 +813,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503305</v>
+        <v>503337</v>
       </c>
       <c r="R3" t="n">
-        <v>6918716</v>
+        <v>6918753</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120062035</v>
+        <v>120062148</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -715,12 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503305</v>
+        <v>503283</v>
       </c>
       <c r="R2" t="n">
-        <v>6918716</v>
+        <v>6918747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -801,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120061827</v>
+        <v>120062394</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503337</v>
+        <v>503250</v>
       </c>
       <c r="R3" t="n">
-        <v>6918753</v>
+        <v>6918811</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120062394</v>
+        <v>120062035</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,41 +920,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503250</v>
+        <v>503305</v>
       </c>
       <c r="R4" t="n">
-        <v>6918811</v>
+        <v>6918716</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,12 +1022,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1137,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120062148</v>
+        <v>120061827</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,50 +1158,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503283</v>
+        <v>503337</v>
       </c>
       <c r="R6" t="n">
-        <v>6918747</v>
+        <v>6918753</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120062148</v>
+        <v>120062035</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -715,7 +715,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503283</v>
+        <v>503305</v>
       </c>
       <c r="R2" t="n">
-        <v>6918747</v>
+        <v>6918716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120062394</v>
+        <v>120062148</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +813,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503250</v>
+        <v>503283</v>
       </c>
       <c r="R3" t="n">
-        <v>6918811</v>
+        <v>6918747</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +910,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120062035</v>
+        <v>120062394</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,55 +934,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503305</v>
+        <v>503250</v>
       </c>
       <c r="R4" t="n">
-        <v>6918716</v>
+        <v>6918811</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,22 +1022,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120061721</v>
+        <v>120061827</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,21 +1050,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503319</v>
+        <v>503337</v>
       </c>
       <c r="R5" t="n">
-        <v>6918782</v>
+        <v>6918753</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120061827</v>
+        <v>120061721</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,21 +1162,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503337</v>
+        <v>503319</v>
       </c>
       <c r="R6" t="n">
-        <v>6918753</v>
+        <v>6918782</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120062035</v>
+        <v>120062394</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503305</v>
+        <v>503250</v>
       </c>
       <c r="R2" t="n">
-        <v>6918716</v>
+        <v>6918811</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120062148</v>
+        <v>120061721</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,50 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503283</v>
+        <v>503319</v>
       </c>
       <c r="R3" t="n">
-        <v>6918747</v>
+        <v>6918782</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120062394</v>
+        <v>120062148</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,41 +911,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503250</v>
+        <v>503283</v>
       </c>
       <c r="R4" t="n">
-        <v>6918811</v>
+        <v>6918747</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120061827</v>
+        <v>120062035</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,41 +1032,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503337</v>
+        <v>503305</v>
       </c>
       <c r="R5" t="n">
-        <v>6918753</v>
+        <v>6918716</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1134,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120061721</v>
+        <v>120061827</v>
       </c>
       <c r="B6" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,21 +1162,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503319</v>
+        <v>503337</v>
       </c>
       <c r="R6" t="n">
-        <v>6918782</v>
+        <v>6918753</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120062394</v>
+        <v>120062035</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503250</v>
+        <v>503305</v>
       </c>
       <c r="R2" t="n">
-        <v>6918811</v>
+        <v>6918716</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120061721</v>
+        <v>120061827</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503319</v>
+        <v>503337</v>
       </c>
       <c r="R3" t="n">
-        <v>6918782</v>
+        <v>6918753</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +916,7 @@
         <v>120062148</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1020,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120062035</v>
+        <v>120061721</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,55 +1046,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503305</v>
+        <v>503319</v>
       </c>
       <c r="R5" t="n">
-        <v>6918716</v>
+        <v>6918782</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1134,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120061827</v>
+        <v>120062394</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503337</v>
+        <v>503250</v>
       </c>
       <c r="R6" t="n">
-        <v>6918753</v>
+        <v>6918811</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120062035</v>
+        <v>120061827</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503305</v>
+        <v>503337</v>
       </c>
       <c r="R2" t="n">
-        <v>6918716</v>
+        <v>6918753</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120061827</v>
+        <v>120062035</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,41 +799,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503337</v>
+        <v>503305</v>
       </c>
       <c r="R3" t="n">
-        <v>6918753</v>
+        <v>6918716</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120061721</v>
+        <v>120062394</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,25 +1046,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503319</v>
+        <v>503250</v>
       </c>
       <c r="R5" t="n">
-        <v>6918782</v>
+        <v>6918811</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120062394</v>
+        <v>120061721</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503250</v>
+        <v>503319</v>
       </c>
       <c r="R6" t="n">
-        <v>6918811</v>
+        <v>6918782</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120062035</v>
+        <v>120062394</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,55 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503305</v>
+        <v>503250</v>
       </c>
       <c r="R3" t="n">
-        <v>6918716</v>
+        <v>6918811</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1034,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120062394</v>
+        <v>120061721</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503250</v>
+        <v>503319</v>
       </c>
       <c r="R5" t="n">
-        <v>6918811</v>
+        <v>6918782</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1109,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120061721</v>
+        <v>120062035</v>
       </c>
       <c r="B6" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,41 +1144,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503319</v>
+        <v>503305</v>
       </c>
       <c r="R6" t="n">
-        <v>6918782</v>
+        <v>6918716</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120061827</v>
+        <v>120061721</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503337</v>
+        <v>503319</v>
       </c>
       <c r="R2" t="n">
-        <v>6918753</v>
+        <v>6918782</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120062394</v>
+        <v>120062035</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503250</v>
+        <v>503305</v>
       </c>
       <c r="R3" t="n">
-        <v>6918811</v>
+        <v>6918716</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120062148</v>
+        <v>120061827</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,50 +925,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503283</v>
+        <v>503337</v>
       </c>
       <c r="R4" t="n">
-        <v>6918747</v>
+        <v>6918753</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120061721</v>
+        <v>120062394</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1037,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503319</v>
+        <v>503250</v>
       </c>
       <c r="R5" t="n">
-        <v>6918782</v>
+        <v>6918811</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120062035</v>
+        <v>120062148</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1172,12 +1177,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503305</v>
+        <v>503283</v>
       </c>
       <c r="R6" t="n">
-        <v>6918716</v>
+        <v>6918747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120061721</v>
+        <v>120061827</v>
       </c>
       <c r="B2" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503319</v>
+        <v>503337</v>
       </c>
       <c r="R2" t="n">
-        <v>6918782</v>
+        <v>6918753</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120062035</v>
+        <v>120061721</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,55 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503305</v>
+        <v>503319</v>
       </c>
       <c r="R3" t="n">
-        <v>6918716</v>
+        <v>6918782</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120061827</v>
+        <v>120062394</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503337</v>
+        <v>503250</v>
       </c>
       <c r="R4" t="n">
-        <v>6918753</v>
+        <v>6918811</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -988,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120062394</v>
+        <v>120062035</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,41 +1023,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503250</v>
+        <v>503305</v>
       </c>
       <c r="R5" t="n">
-        <v>6918811</v>
+        <v>6918716</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,12 +1125,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 39493-2024 artfynd.xlsx
+++ b/artfynd/A 39493-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120061827</v>
+        <v>120062035</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503337</v>
+        <v>503305</v>
       </c>
       <c r="R2" t="n">
-        <v>6918753</v>
+        <v>6918716</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120061721</v>
+        <v>120062394</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503319</v>
+        <v>503250</v>
       </c>
       <c r="R3" t="n">
-        <v>6918782</v>
+        <v>6918811</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120062394</v>
+        <v>120062148</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +925,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503250</v>
+        <v>503283</v>
       </c>
       <c r="R4" t="n">
-        <v>6918811</v>
+        <v>6918747</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1022,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120062035</v>
+        <v>120061721</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,55 +1046,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503305</v>
+        <v>503319</v>
       </c>
       <c r="R5" t="n">
-        <v>6918716</v>
+        <v>6918782</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1134,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120062148</v>
+        <v>120061827</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,50 +1158,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Källmyran, Källmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503283</v>
+        <v>503337</v>
       </c>
       <c r="R6" t="n">
-        <v>6918747</v>
+        <v>6918753</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,12 +1246,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
